--- a/EKG_Kalite_Yönetim_Sistemi/10_Değişiklik ve Geçici Proses Kontrolü/02_Geçici Kontrol, By-pass ve Asıl Prosese Dönüş/EKG-PRJ-FRM-29_gecici_proses_ve_asil_prosese_donus_onay_kaydi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/10_Değişiklik ve Geçici Proses Kontrolü/02_Geçici Kontrol, By-pass ve Asıl Prosese Dönüş/EKG-PRJ-FRM-29_gecici_proses_ve_asil_prosese_donus_onay_kaydi.xlsx
@@ -955,7 +955,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-29&amp;C&amp;"Arial,Regular"&amp;11Geçici Proses ve Asıl Prosese Dönüş Onay Kaydı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 23.09.2026
+Revizyon nedeni: Geçici yöntemin yetkisi, izin sonu, ürün sınırı ve testle asıl prosese dönüşü tek kısa kayıtta toplandı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>